--- a/src/bokun/source/107484 LocalGemTour.xlsx
+++ b/src/bokun/source/107484 LocalGemTour.xlsx
@@ -1909,7 +1909,10 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="55" width="8.71"/>
+    <col customWidth="1" min="1" max="1" width="8.71"/>
+    <col customWidth="1" min="2" max="2" width="21.14"/>
+    <col customWidth="1" min="3" max="3" width="58.43"/>
+    <col customWidth="1" min="4" max="55" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
